--- a/artfynd/A 28854-2019 artfynd.xlsx
+++ b/artfynd/A 28854-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28854-2019 artfynd.xlsx
+++ b/artfynd/A 28854-2019 artfynd.xlsx
@@ -6409,7 +6409,7 @@
         <v>96160387</v>
       </c>
       <c r="B51" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>536035.6368852875</v>
+        <v>536036</v>
       </c>
       <c r="R51" t="n">
-        <v>6941210.827956873</v>
+        <v>6941211</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6482,19 +6482,9 @@
           <t>2021-09-18</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2021-09-18</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">

--- a/artfynd/A 28854-2019 artfynd.xlsx
+++ b/artfynd/A 28854-2019 artfynd.xlsx
@@ -6409,7 +6409,7 @@
         <v>96160387</v>
       </c>
       <c r="B51" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>

--- a/artfynd/A 28854-2019 artfynd.xlsx
+++ b/artfynd/A 28854-2019 artfynd.xlsx
@@ -6409,7 +6409,7 @@
         <v>96160387</v>
       </c>
       <c r="B51" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
